--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="October 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Omar October 2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,57 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F4F7"/>
+        <bgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +83,71 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,525 +513,546 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="75" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Log_In</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Log_Out</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Duration_Formatted</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Decimal_Hours</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Log-In</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Log-Out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Decimal Hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="9" t="n">
         <v>8.25</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="9" t="n">
         <v>8.08</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>7.42</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>05:13 PM</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>9h 23m</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="9" t="n">
         <v>7.8</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>To Be Updated</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
         </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Total October Hours</t>
+        </is>
+      </c>
+      <c r="F15" s="15">
+        <f>SUM(F2:F13)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Omar October 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Timesheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team Leaderboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Team Timesheet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Detailed Timesheet'!$A$1:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Full Team Timesheet'!$A$1:$I$123</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,17 +38,15 @@
     </font>
     <font>
       <name val="Segoe UI"/>
-      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00000000"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -64,14 +67,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="002C3E50"/>
+        <bgColor rgb="002C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+        <bgColor rgb="00F9FAFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,51 +110,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -513,20 +534,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="75" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
@@ -539,523 +561,6565 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Log-In</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Log-Out</t>
+          <t>Log_In</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Log_Out</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Decimal Hours</t>
+          <t>Duration_Formatted</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Decimal_Hours</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="G4" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>07:45 AM</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>8h 15m</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>8.25</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Paid Shift</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>8h 00m</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="G6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>04:05 PM</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>8h 05m</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>8.08</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>7h 25m</t>
         </is>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="G8" s="5" t="n">
         <v>7.42</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>03:20 PM</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>7h 30m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>7.5</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>07:50 AM</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>05:13 PM</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>9h 23m</t>
         </is>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="G10" s="5" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>07:47 AM</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>03:35 PM</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>7h 48m</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>7.8</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>OFF</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>05:05 PM</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>9h 05m</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Total October Hours</t>
-        </is>
-      </c>
-      <c r="F15" s="15">
-        <f>SUM(F2:F13)</f>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>13 Active Days</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>107h 05m</t>
+        </is>
+      </c>
+      <c r="G17" s="11">
+        <f>SUM(G2:G16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Cumulative October Output: 107h 05m (107.09 hrs across 13 shifts)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Employee / Team Member</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Days Logged</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Total Hours</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Avg Daily Hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" s="16" t="n">
+        <v>107.09</v>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>8.24</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" s="19" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>9.369999999999999</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>9.02</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>75.41</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>73.43000000000001</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>55.38</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>7.91</v>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Total / Overall Team</t>
+        </is>
+      </c>
+      <c r="C11" s="9">
+        <f>SUM(C2:C10)</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>SUM(D2:D10)</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>AVERAGE(E2:E10)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I123"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="82" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Log_In</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Log_Out</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Duration_Formatted</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Decimal_Hours</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>02:00 PM</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>6h 15m</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>02:00 PM</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>6h 15m</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Saudia Airlines Training Session (6h 15m) + Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>07:45 AM</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>8h 15m</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>08:48 AM</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>7h 12m</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Paid Shift</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>🏢 Airport Onboarding Shift / Logged in 08:48 AM (7h 12m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>04:05 PM</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>🎓 Etihad IGS Training / Paid Standby</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>03:55 AM</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>03:55 AM</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>03:55 AM</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Morning Airport Ground Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>10h 35m</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>10h 35m</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>10h 35m</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>10.58</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 04:45 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>7h 30m</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>05:13 PM</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>9h 23m</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>05:13 PM</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>9h 23m</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>7h 40m</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>05:13 PM</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>12h 28m</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 05:13 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>7h 40m</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>04:45 AM</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>03:30 PM</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>10h 45m</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 04:45 AM / Logged out 03:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Day Off (Weekly Day Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>08:00 PM</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>12h 10m</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Extended Duty (07:50 AM – 08:00 PM / 12h 05m) — ⚠️ Aircraft Technical Hazard: Fuel Leak Incident</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>07:50 AM</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>05:13 PM</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>9h 23m</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>07:47 AM</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>07:47 AM</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I99" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>12h 05m</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>07:47 AM</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>07:47 AM</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>12h 05m</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I105" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>03:30 AM</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>12h 05m</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:30 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>03:15 AM</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>12h 45m</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>Dawn Shift</t>
+        </is>
+      </c>
+      <c r="I107" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Dawn Flight Departure Handling (Logged in 03:15 AM / Logged out 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>07:47 AM</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>7h 48m</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I109" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="inlineStr">
+        <is>
+          <t>Rasheed Akel</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I111" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Talal</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Mohamed Adnan</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I113" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Tarek Orfhly</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>🛑 Inactive / Terminated (Last active shift: Sep 29, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I115" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Joudi Alghorani</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>Hanan</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I117" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Raboushee</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>Osama Alkabbani</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="I119" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>05:05 PM</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>9h 05m</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 05:05 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>04:30 PM</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>8h 30m</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I121" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Etihad DCS Systems Training &amp; Station Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>8h 00m</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>Omar Elnemr</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>8h 05m</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="I123" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I123"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 05:05 PM)</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:30 PM)</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1140,23 +1140,63 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Official Duty</t>
+          <t>Training / Paid</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 04:00 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>12:13 PM</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>4h 18m</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Training / Paid</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 12:13 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>Total October Hours</t>
         </is>
       </c>
-      <c r="F18" s="12">
-        <f>SUM(F2:F16)</f>
+      <c r="F19" s="12">
+        <f>SUM(F2:F17)</f>
         <v/>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -1167,16 +1167,16 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>12:13 PM</t>
+          <t>12:30 PM</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>4h 18m</t>
+          <t>4h 35m</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>4.3</v>
+        <v>4.58</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 12:13 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 12:30 PM)</t>
         </is>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Omar October 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="October 2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="September 2026" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -749,7 +750,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 1 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -789,7 +790,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Saudi KSA Delegation / Paid Standby</t>
+          <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
         </is>
       </c>
     </row>
@@ -902,7 +903,11 @@
       <c r="F10" s="3" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
@@ -1192,11 +1197,408 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Total October Hours</t>
+          <t>Total October 2026 Hours</t>
         </is>
       </c>
       <c r="F19" s="12">
         <f>SUM(F2:F17)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="75" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Log-In</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Log-Out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Decimal Hours</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>06:30 AM</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>9h 30m</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Standardized</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Standardized 23rd shift: 06:30 AM – 04:00 PM (9.5h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Standard daytime shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>05:40 PM</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9h 25m</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Overtime</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>⚡ Extended shift (+1h 40m overtime)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Standard daytime shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Standard daytime shift (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Standard daytime shift (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>08:15 AM</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7h 45m</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Standard daytime shift (4:00 PM return)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>04:00 PM</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Total September 2026 Hours</t>
+        </is>
+      </c>
+      <c r="F11" s="12">
+        <f>SUM(F2:F9)</f>
         <v/>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -508,8 +523,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="75" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="85" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1194,14 +1209,54 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>En Route / Transit</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>🚌 Transit: Arrived Free Zone 07:03 PM, company bus departed 07:23 PM. En route to DAM airport (Awaiting official log-in).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F19" s="12">
-        <f>SUM(F2:F17)</f>
+      <c r="F20" s="15">
+        <f>SUM(F2:F18)</f>
         <v/>
       </c>
     </row>
@@ -1225,8 +1280,8 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="75" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="85" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1592,12 +1647,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -1222,7 +1222,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>En Route / Transit</t>
+          <t>Official Duty</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
         <is>
-          <t>🚌 Transit: Arrived Free Zone 07:03 PM, company bus departed 07:23 PM. En route to DAM airport (Awaiting official log-in).</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Awaiting Checkout | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
         </is>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1210,52 +1195,52 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>08:00 AM</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>03:37 PM</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>7h 37m</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 08:00 AM / Awaiting Checkout | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 08:00 AM / Logged out 03:37 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="12">
         <f>SUM(F2:F18)</f>
         <v/>
       </c>
@@ -1647,12 +1632,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1234,14 +1234,54 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F20" s="12">
-        <f>SUM(F2:F18)</f>
+      <c r="F21" s="12">
+        <f>SUM(F2:F19)</f>
         <v/>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1274,14 +1289,54 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F21" s="12">
-        <f>SUM(F2:F19)</f>
+      <c r="F22" s="15">
+        <f>SUM(F2:F20)</f>
         <v/>
       </c>
     </row>
@@ -1672,12 +1727,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1290,52 +1275,52 @@
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>03:20 PM</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>7h 25m</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="12">
         <f>SUM(F2:F20)</f>
         <v/>
       </c>
@@ -1727,12 +1712,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -657,20 +657,20 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Training / Paid</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>🎓 Etihad IGS Training Prep / Paid Administrative Standby (8h)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>07:45 AM</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -697,20 +697,20 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>8h 15m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F5" s="9" t="n">
-        <v>8.25</v>
+        <v>9</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Paid Shift</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
         <is>
-          <t>🏢 Airport Onboarding Shift / Logged in 07:45 AM (8h 15m)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1314,14 +1329,54 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F22" s="12">
-        <f>SUM(F2:F20)</f>
+      <c r="F23" s="15">
+        <f>SUM(F2:F21)</f>
         <v/>
       </c>
     </row>
@@ -1712,12 +1767,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1330,52 +1315,52 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>06:24 PM</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>10h 29m</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:55 AM / Logged out 06:24 PM)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="12">
         <f>SUM(F2:F21)</f>
         <v/>
       </c>
@@ -1767,12 +1752,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1354,14 +1369,54 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>07:55 AM</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F23" s="12">
-        <f>SUM(F2:F21)</f>
+      <c r="F24" s="15">
+        <f>SUM(F2:F22)</f>
         <v/>
       </c>
     </row>
@@ -1752,12 +1807,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1370,52 +1355,52 @@
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>07:55 AM</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>04:20 PM</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8h 25m</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Awaiting Checkout)</t>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 04:20 PM)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="12">
         <f>SUM(F2:F22)</f>
         <v/>
       </c>
@@ -1807,12 +1792,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -727,21 +742,21 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -767,21 +782,21 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>04:05 PM</t>
+          <t>04:45 PM</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="F7" s="9" t="n">
-        <v>8.08</v>
+        <v>9.42</v>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
@@ -807,21 +822,21 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7.42</v>
+        <v>8.75</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -830,7 +845,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Airport Ground Station Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Airport Ground Station Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -847,21 +862,21 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>7h 30m</t>
+          <t>8h 50m</t>
         </is>
       </c>
       <c r="F9" s="9" t="n">
-        <v>7.5</v>
+        <v>8.83</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -870,7 +885,7 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -887,21 +902,21 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>07:50 AM</t>
+          <t>07:10 AM</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>05:13 PM</t>
+          <t>05:53 PM</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9h 23m</t>
+          <t>10h 43m</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>9.380000000000001</v>
+        <v>10.72</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -910,7 +925,7 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:50 AM / Logged out 05:13 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 05:53 PM)</t>
         </is>
       </c>
     </row>
@@ -927,21 +942,21 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>07:47 AM</t>
+          <t>07:07 AM</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>03:35 PM</t>
+          <t>04:15 PM</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>7h 48m</t>
+          <t>9h 08m</t>
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>7.8</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -950,7 +965,7 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:47 AM / Logged out 03:35 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:07 AM / Logged out 04:15 PM)</t>
         </is>
       </c>
     </row>
@@ -1007,21 +1022,21 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>05:05 PM</t>
+          <t>05:45 PM</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>9h 10m</t>
+          <t>10h 30m</t>
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>9.17</v>
+        <v>10.5</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -1030,7 +1045,7 @@
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 05:05 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 05:45 PM)</t>
         </is>
       </c>
     </row>
@@ -1047,21 +1062,21 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>04:30 PM</t>
+          <t>05:10 PM</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8h 30m</t>
+          <t>9h 50m</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>8.5</v>
+        <v>9.83</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1070,7 +1085,7 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 05:10 PM)</t>
         </is>
       </c>
     </row>
@@ -1087,21 +1102,21 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>8h 00m</t>
+          <t>9h 20m</t>
         </is>
       </c>
       <c r="F15" s="9" t="n">
-        <v>8</v>
+        <v>9.33</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -1110,7 +1125,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 08:00 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 04:40 PM)</t>
         </is>
       </c>
     </row>
@@ -1127,21 +1142,21 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>04:00 PM</t>
+          <t>04:40 PM</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8h 05m</t>
+          <t>9h 25m</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>8.08</v>
+        <v>9.42</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1150,7 +1165,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 04:00 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 04:40 PM)</t>
         </is>
       </c>
     </row>
@@ -1167,21 +1182,21 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>12:30 PM</t>
+          <t>01:10 PM</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>4h 35m</t>
+          <t>5h 55m</t>
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>4.58</v>
+        <v>5.92</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -1190,7 +1205,7 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:55 AM / Logged out 12:30 PM)</t>
+          <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 01:10 PM)</t>
         </is>
       </c>
     </row>
@@ -1207,21 +1222,21 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>07:20 AM</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>03:37 PM</t>
+          <t>04:17 PM</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7h 37m</t>
+          <t>8h 57m</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>7.62</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1230,7 +1245,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 08:00 AM / Logged out 03:37 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:20 AM / Logged out 04:17 PM | Free Zone Bus: Arr 07:03 PM, Dep 07:23 PM)</t>
         </is>
       </c>
     </row>
@@ -1287,21 +1302,21 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>03:20 PM</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7h 25m</t>
+          <t>8h 45m</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.42</v>
+        <v>8.75</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1310,7 +1325,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 03:20 PM)</t>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 04:00 PM)</t>
         </is>
       </c>
     </row>
@@ -1327,21 +1342,21 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>06:24 PM</t>
+          <t>07:04 PM</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>10h 29m</t>
+          <t>11h 49m</t>
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>10.48</v>
+        <v>11.82</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1350,7 +1365,7 @@
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>⚡ Extended Shift / Overtime (Logged in 07:55 AM / Logged out 06:24 PM)</t>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 07:04 PM)</t>
         </is>
       </c>
     </row>
@@ -1367,21 +1382,21 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>07:55 AM</t>
+          <t>07:15 AM</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>04:20 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8h 25m</t>
+          <t>9h 45m</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>8.42</v>
+        <v>9.75</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1390,18 +1405,58 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Duty (Logged in 07:55 AM / Logged out 04:20 PM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Logged out 05:00 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>07:15 AM</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F24" s="12">
-        <f>SUM(F2:F22)</f>
+      <c r="F25" s="15">
+        <f>SUM(F2:F23)</f>
         <v/>
       </c>
     </row>
@@ -1792,12 +1847,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -116,6 +116,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -123,15 +132,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -622,30 +622,30 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>07:00 AM</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>04:00 PM</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>0h 00m</t>
+          <t>9h 00m</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Day Off</t>
+          <t>Paid Standby</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>🌴 Scheduled Team Rest Day (Contractual 1 Day Off in 7-day cycle)</t>
+          <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
       </c>
     </row>
@@ -690,40 +690,40 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>
@@ -770,40 +770,40 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>07:20 AM</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>04:45 PM</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>9h 25m</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="6" t="n">
         <v>9.42</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>🎓 Etihad IGS Training Day 2 (MS Teams) / Paid Standby</t>
         </is>
@@ -850,40 +850,40 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:10 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>8h 50m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="6" t="n">
         <v>8.83</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:10 AM / Logged out 04:00 PM)</t>
         </is>
@@ -930,120 +930,120 @@
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>07:07 AM</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>04:15 PM</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>9h 08m</t>
         </is>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="6" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>✈️ Live Daily Duty (Logged in 07:07 AM / Logged out 04:15 PM)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Team Weekly Rest Day (Full Station Off)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>07:15 AM</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>05:45 PM</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>10h 30m</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="6" t="n">
         <v>10.5</v>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 05:45 PM)</t>
         </is>
@@ -1090,40 +1090,40 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>07:20 AM</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>04:40 PM</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>9h 20m</t>
         </is>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="6" t="n">
         <v>9.33</v>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:20 AM / Logged out 04:40 PM)</t>
         </is>
@@ -1170,40 +1170,40 @@
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>07:15 AM</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>01:10 PM</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>5h 55m</t>
         </is>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="6" t="n">
         <v>5.92</v>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Training / Paid</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>🎓 Etihad Airways Altéa DCS System Training (Logged in 07:15 AM / Logged out 01:10 PM)</t>
         </is>
@@ -1250,40 +1250,40 @@
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>OFF</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>0h 00m</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>Day Off</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>🌴 Scheduled Rest Day (Off Duty)</t>
         </is>
@@ -1330,40 +1330,40 @@
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>07:15 AM</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>07:04 PM</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>11h 49m</t>
         </is>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="6" t="n">
         <v>11.82</v>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 07:04 PM)</t>
         </is>
@@ -1567,40 +1567,40 @@
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>08:15 AM</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>7h 45m</t>
         </is>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="6" t="n">
         <v>7.75</v>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Standard daytime shift</t>
         </is>
@@ -1647,40 +1647,40 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>08:15 AM</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>7h 45m</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="6" t="n">
         <v>7.75</v>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Standard daytime shift</t>
         </is>
@@ -1727,40 +1727,40 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>08:15 AM</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>7h 45m</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="6" t="n">
         <v>7.75</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>Standard daytime shift (4:00 PM return)</t>
         </is>
@@ -1807,40 +1807,40 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>07:00 AM</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>04:00 PM</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>9h 00m</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Paid Standby</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>🏢 Paid Administrative Standby (Damascus Airport Pass Delay - Company Paid)</t>
         </is>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1410,52 +1395,52 @@
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>07:15 AM</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>06:40 PM</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>11h 25m</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Duty (Logged in 07:15 AM / Awaiting Checkout)</t>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:15 AM / Logged out 06:40 PM)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="12">
         <f>SUM(F2:F23)</f>
         <v/>
       </c>
@@ -1847,12 +1832,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1434,14 +1449,54 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>07:20 AM</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:20 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F25" s="12">
-        <f>SUM(F2:F23)</f>
+      <c r="F26" s="15">
+        <f>SUM(F2:F24)</f>
         <v/>
       </c>
     </row>
@@ -1832,12 +1887,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1450,52 +1435,52 @@
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>07:20 AM</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>07:30 PM</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>12h 10m</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Ground Duty (Logged in 07:20 AM / Awaiting Checkout)</t>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>⚡ Extended Shift / Overtime (Logged in 07:20 AM / Logged out 07:30 PM)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="12">
         <f>SUM(F2:F24)</f>
         <v/>
       </c>
@@ -1887,12 +1872,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1474,14 +1489,54 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>07:24 AM</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F26" s="12">
-        <f>SUM(F2:F24)</f>
+      <c r="F27" s="15">
+        <f>SUM(F2:F25)</f>
         <v/>
       </c>
     </row>
@@ -1872,12 +1927,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1490,52 +1475,52 @@
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>07:24 AM</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>03:00 PM</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>7h 36m</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>Official Duty</t>
         </is>
       </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Awaiting Checkout)</t>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:00 PM)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="12">
         <f>SUM(F2:F25)</f>
         <v/>
       </c>
@@ -1927,12 +1912,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -1492,16 +1492,16 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>03:00 PM</t>
+          <t>03:40 PM</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>7h 36m</t>
+          <t>8h 16m</t>
         </is>
       </c>
       <c r="F25" s="6" t="n">
-        <v>7.6</v>
+        <v>8.27</v>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:00 PM)</t>
+          <t>✈️ Live Daily Ground Duty (Logged in 07:24 AM / Logged out 03:40 PM)</t>
         </is>
       </c>
     </row>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +67,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -126,6 +132,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -499,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1514,14 +1529,54 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>08:00 PM</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>To Be Updated</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Night Shift</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Awaiting Checkout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F27" s="12">
-        <f>SUM(F2:F25)</f>
+      <c r="F28" s="15">
+        <f>SUM(F2:F26)</f>
         <v/>
       </c>
     </row>
@@ -1912,12 +1967,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="15">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -44,7 +44,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,12 +67,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -132,15 +126,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1530,52 +1515,52 @@
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-10-25</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>08:00 PM</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>To Be Updated</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>03:10 AM</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7h 10m</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Night Shift</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Awaiting Checkout)</t>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>✈️ Live Airport Ground Station Night Duty (Logged in 08:00 PM / Logged out 03:10 AM next day)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="12">
         <f>SUM(F2:F26)</f>
         <v/>
       </c>
@@ -1967,12 +1952,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Total September 2026 Hours</t>
         </is>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="12">
         <f>SUM(F2:F9)</f>
         <v/>
       </c>

--- a/omar_elnemr_attendance_october_2026.xlsx
+++ b/omar_elnemr_attendance_october_2026.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1554,14 +1554,134 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>9h 00m</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Paid Standby</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>🏢 Company Paid Standby (Flight Cancelled - Station Standby)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>0h 00m</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Day Off</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>🌴 Scheduled Rest Day (Off Duty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>08:20 AM</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>03:35 PM</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>7h 15m</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Official Duty</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>✈️ Live Daily Ground Duty (Logged in 08:20 AM / Logged out 03:35 PM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Total October 2026 Hours</t>
         </is>
       </c>
-      <c r="F28" s="12">
-        <f>SUM(F2:F26)</f>
+      <c r="F31" s="12">
+        <f>SUM(F2:F29)</f>
         <v/>
       </c>
     </row>
